--- a/labs/lab-07-custom-dashboard-skill/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
+++ b/labs/lab-07-custom-dashboard-skill/data/checkpoints/Northstar_Verified_Checkpoint.xlsx
@@ -13,20 +13,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter_Lists" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=".Rules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_Summaries" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter_Lists" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Dashboard'!$A$1:$D$38</definedName>
+    <definedName name="Slicer_Site">#N/A</definedName>
+    <definedName name="Slicer_Job_Category">#N/A</definedName>
+    <definedName name="Slicer_Status">#N/A</definedName>
+    <definedName name="Slicer_Assigned_To">#N/A</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
+      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicerCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSlicerCache1"/>
+        <x14:slicerCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSlicerCache2"/>
+        <x14:slicerCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSlicerCache3"/>
+        <x14:slicerCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSlicerCache4"/>
+      </x15:slicerCaches>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -37,7 +46,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;S$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +58,59 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +122,33 @@
         <fgColor rgb="001F6FEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A9D8F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -71,11 +156,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="002E75B6"/>
+      </left>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="thin">
+        <color rgb="002E75B6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="002E75B6"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00C9D3E3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thick">
+        <color rgb="00FFFFFF"/>
+      </right>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -101,10 +213,112 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -182,18 +396,34 @@
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Work orders by status</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Dashboard_Summaries'!$O$4</f>
+          <strCache>
+            <ptCount val="1"/>
+            <pt idx="0">
+              <v>Closed is the largest status group (48 of 120)</v>
+            </pt>
+          </strCache>
+        </strRef>
       </tx>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1300" b="1">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr sz="1300" b="1">
+            <a:solidFill>
+              <a:srgbClr val="404040"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
     </title>
     <plotArea>
       <barChart>
@@ -204,26 +434,54 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B15</f>
+              <f>'Dashboard_Summaries'!B3</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$16:$A$21</f>
+              <f>'Dashboard_Summaries'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$16:$B$21</f>
+              <f>'Dashboard_Summaries'!$B$4:$B$9</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <numFmt formatCode="0;;;" sourceLinked="0"/>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="404040"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+        </dLbls>
+        <gapWidth val="50"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -232,9 +490,27 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -243,16 +519,13 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -264,59 +537,121 @@
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Work orders by category</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Dashboard_Summaries'!$O$5</f>
+          <strCache>
+            <ptCount val="1"/>
+            <pt idx="0">
+              <v>All five job categories are level at 24 work orders</v>
+            </pt>
+          </strCache>
+        </strRef>
       </tx>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1300" b="1">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr sz="1300" b="1">
+            <a:solidFill>
+              <a:srgbClr val="404040"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
+        <barDir val="bar"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B24</f>
+              <f>'Dashboard_Summaries'!E3</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E75B6"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$25:$A$29</f>
+              <f>'Dashboard_Summaries'!$D$4:$D$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$25:$B$29</f>
+              <f>'Dashboard_Summaries'!$E$4:$E$8</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <numFmt formatCode="0;;;" sourceLinked="0"/>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="404040"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+        </dLbls>
+        <gapWidth val="50"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -325,16 +660,13 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -346,59 +678,203 @@
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Work orders by site</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Dashboard_Summaries'!$O$6</f>
+          <strCache>
+            <ptCount val="1"/>
+            <pt idx="0">
+              <v>Changi Workshop has the most overdue backlog (18 of 50)</v>
+            </pt>
+          </strCache>
+        </strRef>
       </tx>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1300" b="1">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr sz="1300" b="1">
+            <a:solidFill>
+              <a:srgbClr val="404040"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B33</f>
+              <f>'Dashboard_Summaries'!H3</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$34:$A$38</f>
+              <f>'Dashboard_Summaries'!$G$4:$G$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$34:$B$38</f>
+              <f>'Dashboard_Summaries'!$H$4:$H$8</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard_Summaries'!I3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E75B6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard_Summaries'!$G$4:$G$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard_Summaries'!$I$4:$I$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard_Summaries'!J3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2A9D8F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard_Summaries'!$G$4:$G$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard_Summaries'!$J$4:$J$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard_Summaries'!K3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="A6A6A6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard_Summaries'!$G$4:$G$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard_Summaries'!$K$4:$K$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="0;;;" sourceLinked="0"/>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </txPr>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+        </dLbls>
+        <gapWidth val="50"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -407,15 +883,32 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="404040"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="404040"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -424,15 +917,15 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="2880000"/>
+    <ext cx="4942857" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -449,12 +942,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="2880000"/>
+    <ext cx="4942857" cy="2951999"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -471,12 +964,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="2880000"/>
+    <ext cx="9885714" cy="3096000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -491,7 +984,340 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2038350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="100" name="Site"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Site"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="2300000" cy="1600000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers need Excel 2013 or later.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2038350</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="101" name="Job_Category"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Job_Category"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="2300000" cy="1600000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers need Excel 2013 or later.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2038350</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="102" name="Status"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Status"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="2300000" cy="1600000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers need Excel 2013 or later.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2038350</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="103" name="Assigned_To"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Assigned_To"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="2300000" cy="1600000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers need Excel 2013 or later.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </wsDr>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Site" sourceName="Site">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="1" column="2"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Job_Category" sourceName="Job_Category">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="1" column="3"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Status" sourceName="Status">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="1" column="5"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Assigned_To" sourceName="Assigned_To">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="1" column="6"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Site" cache="Slicer_Site" caption="Site" columnCount="1" style="SlicerStyleLight1" rowHeight="225425"/>
+  <slicer name="Job_Category" cache="Slicer_Job_Category" caption="Job Category" columnCount="1" style="SlicerStyleLight1" rowHeight="225425"/>
+  <slicer name="Status" cache="Slicer_Status" caption="Status" columnCount="2" style="SlicerStyleLight1" rowHeight="225425"/>
+  <slicer name="Assigned_To" cache="Slicer_Assigned_To" caption="Assigned To" columnCount="2" style="SlicerStyleLight1" rowHeight="225425"/>
+</slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -896,7 +1722,710 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Dashboard chart summaries, titles and checks (formula-backed; same selection as Dashboard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>Work orders</t>
+        </is>
+      </c>
+      <c r="D3" s="38" t="inlineStr">
+        <is>
+          <t>Job category</t>
+        </is>
+      </c>
+      <c r="E3" s="38" t="inlineStr">
+        <is>
+          <t>Work orders</t>
+        </is>
+      </c>
+      <c r="G3" s="38" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="H3" s="38" t="inlineStr">
+        <is>
+          <t>Overdue backlog</t>
+        </is>
+      </c>
+      <c r="I3" s="38" t="inlineStr">
+        <is>
+          <t>Other backlog</t>
+        </is>
+      </c>
+      <c r="J3" s="38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K3" s="38" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="L3" s="38" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N3" s="38" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="O3" s="38" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]=A4))</f>
+        <v/>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="E4">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Job_Category]=D4))</f>
+        <v/>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="H4">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Due_Date]&lt;Control!$B$2)*(tblWorkOrders[Site]=G4))</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Site]=G4))-H4</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed")*(tblWorkOrders[Site]=G4))</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Cancelled")*(tblWorkOrders[Site]=G4))</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>SUM(H4:K4)</f>
+        <v/>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Status chart title</t>
+        </is>
+      </c>
+      <c r="O4">
+        <f>IF(Dashboard!$B$7=0,"No work orders in the current selection",IF(COUNTIF(B4:B9,MAX(B4:B9))&gt;1,COUNTIF(B4:B9,MAX(B4:B9))&amp;" statuses tie for most work orders ("&amp;MAX(B4:B9)&amp;" each)",INDEX(A4:A9,MATCH(MAX(B4:B9),B4:B9,0))&amp;" is the largest status group ("&amp;MAX(B4:B9)&amp;" of "&amp;Dashboard!$B$7&amp;")"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]=A5))</f>
+        <v/>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Job_Category]=D5))</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="H5">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Due_Date]&lt;Control!$B$2)*(tblWorkOrders[Site]=G5))</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Site]=G5))-H5</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed")*(tblWorkOrders[Site]=G5))</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Cancelled")*(tblWorkOrders[Site]=G5))</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>SUM(H5:K5)</f>
+        <v/>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Category chart title</t>
+        </is>
+      </c>
+      <c r="O5">
+        <f>IF(Dashboard!$B$7=0,"No work orders in the current selection",IF(MAX(E4:E8)=MIN(E4:E8),"All five job categories are level at "&amp;MAX(E4:E8)&amp;" work orders",IF(COUNTIF(E4:E8,MAX(E4:E8))&gt;1,COUNTIF(E4:E8,MAX(E4:E8))&amp;" categories tie for most work orders ("&amp;MAX(E4:E8)&amp;" each)",INDEX(D4:D8,MATCH(MAX(E4:E8),E4:E8,0))&amp;" has the most work orders ("&amp;MAX(E4:E8)&amp;")")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]=A6))</f>
+        <v/>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="E6">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Job_Category]=D6))</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="H6">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Due_Date]&lt;Control!$B$2)*(tblWorkOrders[Site]=G6))</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Site]=G6))-H6</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed")*(tblWorkOrders[Site]=G6))</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Cancelled")*(tblWorkOrders[Site]=G6))</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>SUM(H6:K6)</f>
+        <v/>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Site chart title</t>
+        </is>
+      </c>
+      <c r="O6">
+        <f>IF(H9=0,"No overdue backlog in the current selection",IF(COUNTIF(H4:H8,MAX(H4:H8))&gt;1,COUNTIF(H4:H8,MAX(H4:H8))&amp;" sites tie for most overdue backlog ("&amp;MAX(H4:H8)&amp;" each)",INDEX(G4:G8,MATCH(MAX(H4:H8),H4:H8,0))&amp;" has the most overdue backlog ("&amp;MAX(H4:H8)&amp;" of "&amp;H9&amp;")"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]=A7))</f>
+        <v/>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="E7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Job_Category]=D7))</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="H7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Due_Date]&lt;Control!$B$2)*(tblWorkOrders[Site]=G7))</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Site]=G7))-H7</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed")*(tblWorkOrders[Site]=G7))</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Cancelled")*(tblWorkOrders[Site]=G7))</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>SUM(H7:K7)</f>
+        <v/>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Unassigned backlog</t>
+        </is>
+      </c>
+      <c r="O7">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Assigned_To]=""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]=A8))</f>
+        <v/>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="E8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Job_Category]=D8))</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="H8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Due_Date]&lt;Control!$B$2)*(tblWorkOrders[Site]=G8))</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Site]=G8))-H8</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed")*(tblWorkOrders[Site]=G8))</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Cancelled")*(tblWorkOrders[Site]=G8))</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>SUM(H8:K8)</f>
+        <v/>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Closed on or before due date</t>
+        </is>
+      </c>
+      <c r="O8">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed")*(tblWorkOrders[Closed_Date]&lt;=tblWorkOrders[Due_Date]))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]=A9))</f>
+        <v/>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E9" s="39">
+        <f>SUM(E4:E8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H9" s="39">
+        <f>SUM(H4:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="39">
+        <f>SUM(I4:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="39">
+        <f>SUM(J4:J8)</f>
+        <v/>
+      </c>
+      <c r="K9" s="39">
+        <f>SUM(K4:K8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="39">
+        <f>SUM(L4:L8)</f>
+        <v/>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Baseline view (All, no slicer)</t>
+        </is>
+      </c>
+      <c r="O9">
+        <f>AND(Dashboard!$B$2="All",Dashboard!$B$3="All",Dashboard!$B$4="All",Dashboard!$B$5="All",SUBTOTAL(103,tblWorkOrders[Work_Order_ID])=ROWS(tblWorkOrders[Work_Order_ID]))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="39">
+        <f>SUM(B4:B9)</f>
+        <v/>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Charts reconcile to B7</t>
+        </is>
+      </c>
+      <c r="O10">
+        <f>AND(B10=Dashboard!$B$7,E9=Dashboard!$B$7,L9=Dashboard!$B$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Check: total work orders</t>
+        </is>
+      </c>
+      <c r="O11">
+        <f>IF(AND(O10,OR(NOT(O9),Dashboard!$B$7=Control!$B$3)),"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Check: backlog</t>
+        </is>
+      </c>
+      <c r="O12">
+        <f>IF(AND(Dashboard!$B$7=Dashboard!$B$8+Dashboard!$B$10+B9,OR(NOT(O9),Dashboard!$B$8=Control!$B$6)),"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Check: overdue backlog</t>
+        </is>
+      </c>
+      <c r="O13">
+        <f>IF(AND(Dashboard!$B$9&lt;=Dashboard!$B$8,H9=Dashboard!$B$9,OR(NOT(O9),Dashboard!$B$9=Control!$B$7)),"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Check: closed</t>
+        </is>
+      </c>
+      <c r="O14">
+        <f>IF(AND(Dashboard!$B$10=B8,OR(NOT(O9),Dashboard!$B$10=Control!$B$4)),"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Check: on-time rate</t>
+        </is>
+      </c>
+      <c r="O15">
+        <f>IF(Dashboard!$B$10=0,IF(Dashboard!$B$11="N/A","PASS","REVIEW"),IF(AND(ROUND(O8/Dashboard!$B$10-Dashboard!$B$11,6)=0,OR(NOT(O9),ROUND(Dashboard!$B$11-Control!$B$10,6)=0)),"PASS","REVIEW"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Check: recorded cost</t>
+        </is>
+      </c>
+      <c r="O16">
+        <f>IF(AND(ROUND(Dashboard!$B$12-SUMPRODUCT(((tblWorkOrders[Site]=Dashboard!$B$2)+(Dashboard!$B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=Dashboard!$B$3)+(Dashboard!$B$3="All")&gt;0)*((tblWorkOrders[Status]=Dashboard!$B$4)+(Dashboard!$B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=Dashboard!$B$5)+(Dashboard!$B$5="All")+((Dashboard!$B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0)),tblWorkOrders[Cost_SGD]),2)=0,OR(NOT(O9),ROUND(Dashboard!$B$12-Control!$B$11,2)=0)),"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>B10&lt;&gt;Dashboard!$B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>E9&lt;&gt;Dashboard!$B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L9">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>L9&lt;&gt;Dashboard!$B$7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1666,7 +3195,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="6" t="n">
         <v>46278</v>
       </c>
@@ -2306,7 +3835,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n"/>
       <c r="G26" s="6" t="n">
         <v>46266</v>
       </c>
@@ -3594,7 +5123,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n"/>
       <c r="G50" s="6" t="n">
         <v>46242</v>
       </c>
@@ -4882,7 +6411,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="n"/>
       <c r="G74" s="6" t="n">
         <v>46218</v>
       </c>
@@ -5522,7 +7051,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="n"/>
       <c r="G86" s="6" t="n">
         <v>46286</v>
       </c>
@@ -6810,7 +8339,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="n"/>
       <c r="G110" s="6" t="n">
         <v>46262</v>
       </c>
@@ -7425,7 +8954,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7631,7 +9159,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7813,7 +9340,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7881,7 +9407,7 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>MICROSOFT 365 COPILOT WEB:
-Write complete water-service-dashboard SKILL.md with YAML name/description. Require actual tblWorkOrders and report date in Control!B2; read visible .Rules. Preserve source IDs/statuses/owners, Technicians, Control, .Rules, Prompt_Log, Pareto_* and unrelated sheets. Plan first and ask before replacing only named dashboard outputs; rerun without duplicated charts. Dashboard B2:B5 select Site, Job_Category, Status, Assigned_To with All bypasses and AND logic. B7 total, B8 backlog excluding Closed/Cancelled, B9 backlog Due_Date before Control!B2, B10 Closed, B11 on-time Closed_Date&lt;=Due_Date among Closed only with N/A if none, B12 recorded Cost_SGD across selected statuses. Create three formula-backed editable status/category/site charts sharing the exact filter scope. Use structured references, not fixed120-row ranges, and white/navy/blue/teal workbook design. Baseline check at 2026-09-30 All:120 total,48 Closed,12 Cancelled,60 backlog,50 overdue,30/48 on-time,35827.50 cost. Verify site/no-Closed/no-row tests, source preservation and a separate two-row append sandbox with 122 total,49 Closed,61 backlog,51 overdue,31/49 on-time and 36227.50 cost. These are snapshot tests, not universal future figures. Ask for missing inputs; never approve assignments, infer causes/savings or send email. Return the entire file.</t>
+Write complete water-service-dashboard SKILL.md with YAML name/description. Require actual tblWorkOrders and report date in Control!B2; read visible .Rules. Preserve source IDs/statuses/owners, Technicians, Control, .Rules, Prompt_Log, Pareto_* and unrelated sheets. Plan first and ask before replacing only named dashboard outputs; rerun without duplicated charts. Dashboard B2:B5 select Site, Job_Category, Status, Assigned_To with All bypasses and AND logic. B7 total, B8 backlog excluding Closed/Cancelled, B9 backlog Due_Date before Control!B2, B10 Closed, B11 on-time Closed_Date&lt;=Due_Date among Closed only with N/A if none, B12 recorded Cost_SGD across selected statuses. Follow visible .Rules DASHBOARD LAYOUT and STYLE: title A1; six KPI tiles in D4:I7 with Checks: PASS; three formula-backed charts (status column, category bar, full-width stacked site bar) with finding-led titles linked to Dashboard_Summaries; slicers for Site, Job_Category, Status and Assigned_To that filter every tile and chart through SUBTOTAL visibility. Use structured references, not fixed 120-row ranges, and never merge cells. Baseline check at 2026-09-30 All:120 total,48 Closed,12 Cancelled,60 backlog,50 overdue,30/48 on-time,35827.50 cost. Verify site/no-Closed/no-row tests, source preservation and a separate two-row append sandbox with 122 total,49 Closed,61 backlog,51 overdue,31/49 on-time and 36227.50 cost. These are snapshot tests, not universal future figures. Ask for missing inputs; never approve assignments, infer causes/savings or send email. Return the entire file.</t>
         </is>
       </c>
     </row>
@@ -7994,7 +9520,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8040,10 +9565,9 @@
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
         <v/>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8054,100 +9578,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>## SOURCE AND SCOPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Preserve Work_Orders, tblWorkOrders, Technicians, current Assigned_To values and source IDs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Use the reporting date from Control!B2. State the selected Site, Job_Category, Status and Assigned_To scope beside every report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Backlog excludes Closed and Cancelled. Overdue backlog has Due_Date strictly before Control!B2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>On-time closure rate uses Closed rows only, with Closed_Date &lt;= Due_Date. Display N/A when no Closed rows remain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>## FORMATS AND VISUALS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Display recorded Cost_SGD as S$ with two decimals; keep underlying values exact. Show dates as DD-MMM-YYYY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Use white backgrounds, navy titles, blue and teal accents, readable labels and named units; never use colour alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>## OUTPUT AND REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8161,495 +9650,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Northstar Maintenance Dashboard</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>As at</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>## SOURCE AND SCOPE</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+          <t>Preserve Work_Orders, tblWorkOrders, Technicians, current Assigned_To values and source IDs.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Job_Category</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+          <t>Use the reporting date from Control!B2. State the selected Site, Job_Category, Status and Assigned_To scope beside every report.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+          <t>Backlog excludes Closed and Cancelled. Overdue backlog has Due_Date strictly before Control!B2.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Assigned_To</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+          <t>On-time closure rate uses Closed rows only, with Closed_Date &lt;= Due_Date. Display N/A when no Closed rows remain.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Measure</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Current selection</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+          <t>## FORMATS AND VISUALS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Total work orders</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Work_Order_ID]&lt;&gt;""))</f>
-        <v/>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
+          <t>Display recorded Cost_SGD as S$ with two decimals; keep underlying values exact. Show dates as DD-MMM-YYYY.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]&lt;&gt;"Closed")*--(tblWorkOrders[Status]&lt;&gt;"Cancelled"))</f>
-        <v/>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+          <t>Use white backgrounds, navy titles, blue and teal accents, readable labels and named units; never use colour alone.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Overdue backlog</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]&lt;&gt;"Closed")*--(tblWorkOrders[Status]&lt;&gt;"Cancelled")*--(tblWorkOrders[Due_Date]&lt;Control!$B$2))</f>
-        <v/>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+          <t>## DASHBOARD LAYOUT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]="Closed"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+          <t>Dashboard sheet: title in A1; Site, Job_Category, Status and Assigned_To dropdowns in B2:B5 (All plus source values); the six measures in B7:B12; data-as-at date and selected scope in D2.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>On-time closure rate</t>
-        </is>
-      </c>
-      <c r="B11" s="7">
-        <f>IF(B10=0,"N/A",SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]="Closed")*--(tblWorkOrders[Closed_Date]&lt;=tblWorkOrders[Due_Date]))/B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+          <t>Six KPI tiles in D4:I7, one column per tile: title in row 4, large value in row 5, short definition in row 6 and "Checks: PASS" in row 7.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Cost SGD</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*tblWorkOrders[Cost_SGD])</f>
-        <v/>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+          <t>Charts in a grid below the tiles: work orders by status and by job category side by side, then a full-width stacked bar by site (overdue backlog, other backlog, Closed, Cancelled).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Slicers for Site, Job_Category, Status and Assigned_To on the right of the tiles, connected to tblWorkOrders. KPI formulas use SUBTOTAL visibility so slicers and dropdowns both filter every tile and chart.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Put chart summaries, chart-title formulas and KPI checks on Dashboard_Summaries. Never merge cells. Hide gridlines on Dashboard.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Work orders by status</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+          <t>## DASHBOARD STYLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]=A16))</f>
-        <v/>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+          <t>Tiles: white bold text on solid navy #1F4E79 (totals and rates), blue #2E75B6 (backlog, overdue) or teal #2A9D8F (Closed, cost).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="B17" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]=A17))</f>
-        <v/>
-      </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+          <t>Every chart title states the finding from a cell formula, e.g. "Changi Workshop has the most overdue backlog (18 of 50)".</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]=A18))</f>
-        <v/>
-      </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
+          <t>Show data labels on bars; no gridlines; rates as % with one decimal. Each chart total must equal B7.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]=A19))</f>
-        <v/>
-      </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+          <t>## OUTPUT AND REVIEW</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="B20" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]=A20))</f>
-        <v/>
-      </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+          <t>Use structured table references. Preserve the visible .Rules sheet and unrelated sheets, charts and Prompt_Log.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="B21" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Status]=A21))</f>
+          <t>Keep current owners separate from unapproved assignment proposals. Missing facts and approvals remain UNKNOWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Ask before replacing named output sheets. Reconcile every count, rate and chart against source rows; do not duplicate outputs on rerun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <f>"Reporting date: "&amp;TEXT(Control!B2,"yyyy-mm-dd")</f>
         <v/>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Work orders by category</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Leak Repair</t>
-        </is>
-      </c>
-      <c r="B25" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Job_Category]=A25))</f>
-        <v/>
-      </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Valve Repair</t>
-        </is>
-      </c>
-      <c r="B26" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Job_Category]=A26))</f>
-        <v/>
-      </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Pipe Replacement</t>
-        </is>
-      </c>
-      <c r="B27" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Job_Category]=A27))</f>
-        <v/>
-      </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Pump Service</t>
-        </is>
-      </c>
-      <c r="B28" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Job_Category]=A28))</f>
-        <v/>
-      </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Meter Service</t>
-        </is>
-      </c>
-      <c r="B29" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Job_Category]=A29))</f>
-        <v/>
-      </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Work orders by site</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Woodlands Hub</t>
-        </is>
-      </c>
-      <c r="B34" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Site]=A34))</f>
-        <v/>
-      </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Jurong Depot</t>
-        </is>
-      </c>
-      <c r="B35" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Site]=A35))</f>
-        <v/>
-      </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Tampines Centre</t>
-        </is>
-      </c>
-      <c r="B36" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Site]=A36))</f>
-        <v/>
-      </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Paya Lebar Office</t>
-        </is>
-      </c>
-      <c r="B37" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Site]=A37))</f>
-        <v/>
-      </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Changi Workshop</t>
-        </is>
-      </c>
-      <c r="B38" s="2">
-        <f>SUMPRODUCT((IF($B$2="All",1,--(tblWorkOrders[Site]=$B$2)))*(IF($B$3="All",1,--(tblWorkOrders[Job_Category]=$B$3)))*(IF($B$4="All",1,--(tblWorkOrders[Status]=$B$4)))*(IF($B$5="All",1,--(tblWorkOrders[Assigned_To]=$B$5)))*--(tblWorkOrders[Site]=A38))</f>
-        <v/>
-      </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D38"/>
-  <dataValidations count="4">
-    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>'Filter_Lists'!$A$1:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>'Filter_Lists'!$B$1:$B$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>'Filter_Lists'!$C$1:$C$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>'Filter_Lists'!$D$1:$D$10</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8659,169 +9827,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="9">
+        <f>"Northstar Maintenance Dashboard — Q3 work orders to "&amp;TEXT(Control!$B$2,"dd-mmm-yyyy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D2" s="12">
+        <f>"Data as at "&amp;TEXT(Control!$B$2,"yyyy-mm-dd")&amp;"   ·   Site: "&amp;$B$2&amp;"  ·  Category: "&amp;$B$3&amp;"  ·  Status: "&amp;$B$4&amp;"  ·  Owner: "&amp;$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Job_Category</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D3" s="13">
+        <f>IF(SUBTOTAL(103,tblWorkOrders[Work_Order_ID])&lt;ROWS(tblWorkOrders[Work_Order_ID]),"⚠ Slicer filter active: "&amp;SUBTOTAL(103,tblWorkOrders[Work_Order_ID])&amp;" of "&amp;ROWS(tblWorkOrders[Work_Order_ID])&amp;" source rows included. Clear the slicers for the full baseline.","All "&amp;ROWS(tblWorkOrders[Work_Order_ID])&amp;" source rows available (no slicer filter).")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Total work orders</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Overdue backlog</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>On-time closure rate</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Recorded cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Assigned_To</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Woodlands Hub</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Leak Repair</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Aisha Tan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jurong Depot</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Valve Repair</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ben Lim</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tampines Centre</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pipe Replacement</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chloe Goh</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Paya Lebar Office</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pump Service</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Daniel Lee</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Changi Workshop</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Meter Service</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="D5" s="17">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="G5" s="19">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="H5" s="20">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Current selection</t>
+        </is>
+      </c>
+      <c r="D6" s="23">
+        <f>"Selected of "&amp;ROWS(tblWorkOrders[Work_Order_ID])&amp;" rows in tblWorkOrders"</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>IF(B7=0,"No rows selected",TEXT(B8/B7,"0%")&amp;" of selection; "&amp;Dashboard_Summaries!O7&amp;" unassigned")</f>
+        <v/>
+      </c>
+      <c r="F6" s="24">
+        <f>"Backlog due before "&amp;TEXT(Control!$B$2,"dd-mmm-yyyy")</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>"Cancelled in selection: "&amp;Dashboard_Summaries!B9</f>
+        <v/>
+      </c>
+      <c r="H6" s="23">
+        <f>IF(B10=0,"No closed jobs in selection",Dashboard_Summaries!O8&amp;" of "&amp;B10&amp;" closed by due date")</f>
+        <v/>
+      </c>
+      <c r="I6" s="25">
+        <f>"Cost_SGD, all statuses; not a budget"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Total work orders</t>
+        </is>
+      </c>
+      <c r="B7" s="27">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=$B$2)+($B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=$B$3)+($B$3="All")&gt;0)*((tblWorkOrders[Status]=$B$4)+($B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=$B$5)+($B$5="All")+(($B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0)))</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>"Checks: "&amp;Dashboard_Summaries!O11</f>
+        <v/>
+      </c>
+      <c r="E7" s="29">
+        <f>"Checks: "&amp;Dashboard_Summaries!O12</f>
+        <v/>
+      </c>
+      <c r="F7" s="29">
+        <f>"Checks: "&amp;Dashboard_Summaries!O13</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>"Checks: "&amp;Dashboard_Summaries!O14</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
+        <f>"Checks: "&amp;Dashboard_Summaries!O15</f>
+        <v/>
+      </c>
+      <c r="I7" s="30">
+        <f>"Checks: "&amp;Dashboard_Summaries!O16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="10" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="B8" s="27">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=$B$2)+($B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=$B$3)+($B$3="All")&gt;0)*((tblWorkOrders[Status]=$B$4)+($B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=$B$5)+($B$5="All")+(($B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Overdue backlog</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=$B$2)+($B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=$B$3)+($B$3="All")&gt;0)*((tblWorkOrders[Status]=$B$4)+($B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=$B$5)+($B$5="All")+(($B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]&lt;&gt;"Closed")*(tblWorkOrders[Status]&lt;&gt;"Cancelled")*(tblWorkOrders[Due_Date]&lt;Control!$B$2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Elena Ong</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Farid Rahman</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Grace Ng</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Hari Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B10" s="27">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=$B$2)+($B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=$B$3)+($B$3="All")&gt;0)*((tblWorkOrders[Status]=$B$4)+($B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=$B$5)+($B$5="All")+(($B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0))*(tblWorkOrders[Status]="Closed"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>On-time closure rate</t>
+        </is>
+      </c>
+      <c r="B11" s="31">
+        <f>IF(B10=0,"N/A",Dashboard_Summaries!O8/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Recorded cost (S$)</t>
+        </is>
+      </c>
+      <c r="B12" s="32">
+        <f>SUMPRODUCT(((tblWorkOrders[Site]=$B$2)+($B$2="All")&gt;0)*((tblWorkOrders[Job_Category]=$B$3)+($B$3="All")&gt;0)*((tblWorkOrders[Status]=$B$4)+($B$4="All")&gt;0)*((tblWorkOrders[Assigned_To]=$B$5)+($B$5="All")+(($B$5="Unassigned")*(tblWorkOrders[Assigned_To]=""))&gt;0)*SUBTOTAL(103,OFFSET(tblWorkOrders[[#Headers],[Work_Order_ID]],ROW(tblWorkOrders[Work_Order_ID])-ROW(tblWorkOrders[[#Headers],[Work_Order_ID]]),0)),tblWorkOrders[Cost_SGD])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>Rows after slicers</t>
+        </is>
+      </c>
+      <c r="B13" s="34">
+        <f>SUBTOTAL(103,tblWorkOrders[Work_Order_ID])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>How to filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>• Dropdowns B2:B5 or the slicers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  both filter every tile and chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>• Unassigned = blank Assigned_To.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>• Baseline: all All, slicers cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>• Summaries + checks:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dashboard_Summaries sheet.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT($D$3,1)="⚠"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Choose from the list" error="Pick All or a value from the dropdown." type="list">
+      <formula1>'Filter_Lists'!$A$1:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Choose from the list" error="Pick All or a value from the dropdown." type="list">
+      <formula1>'Filter_Lists'!$B$1:$B$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Choose from the list" error="Pick All or a value from the dropdown." type="list">
+      <formula1>'Filter_Lists'!$C$1:$C$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Choose from the list" error="Pick All or a value from the dropdown." type="list">
+      <formula1>'Filter_Lists'!$D$1:$D$10</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
+      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicer xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSlicer1"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>